--- a/draftTAPPs/PCD-AFM_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/PCD-AFM_TAPP_draft_v2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Advanced</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>URI / IGSN</t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sampling Unit</t>
+          <t>Sampling Unit Type</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The physical subdivision of the sample to which one row of reported values corresponds — the unit that is analysed and reported, as distinct from the sample as a whole. Where units nest (e.g. confined tracks within grains), state both levels.</t>
+          <t>The kind of physical subdivision of the sample to which one row of reported values corresponds — the unit that is analysed and reported, as distinct from the sample as a whole. Where units nest (e.g. confined tracks within grains), state both levels. The units themselves are listed in Sampling Unit Name.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1592,32 +1592,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sample Preparation Method</t>
+          <t>Sampling Unit Name</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The form in which the sample is presented to the instrument, and the preparation that brought it to that form — for example mounting, sectioning, polishing, coating, crushing, fusion, or extraction of an electron-transparent section. Record 'None' where the material is analysed as received.</t>
+          <t>The name or label of each sampling unit analysed in this session, as the laboratory records it, together with the sample it belongs to — e.g. a spot number, a grain label, a map or region-of-interest name, or an aliquot identifier. Where units are too numerous to name individually, such as map pixels or reconstructed voxels, name the acquisition area they belong to instead.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Polished section | Thin section (unmounted) | Loose particulate on substrate | As-received fragment | Pressed pellet | N/A | None</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1627,29 +1622,29 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>defines: sample &gt; sampling unit</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Gives every field keyed by sampling unit a row to attach its values to, and ties each unit to the sample it belongs to; without it those fields collapse to one value per session.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sampling Unit Selection Criteria</t>
+          <t>Sample Preparation Method</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The rules governing which sampling unit(s) within a sample are selected for analysis, and why. Covers the criteria applied when choosing grains, aliquots, spots, or a region of interest — size, morphology, clarity, freedom from inclusions or alteration, phase identity, or spatial position. Distinct from Target Material, which states the material type the procedure is designed for, and from Sampling Unit, which names the kind of subdivision one row of reported values corresponds to: this field states how, within such a sample, the unit actually analysed is picked out.</t>
+          <t>The form in which the sample is presented to the instrument, and the preparation that brought it to that form — for example mounting, sectioning, polishing, coating, crushing, fusion, or extraction of an electron-transparent section. Record 'None' where the material is analysed as received.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1664,12 +1659,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>Controlled list / Text</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Polished section | Thin section (unmounted) | Loose particulate on substrate | As-received fragment | Pressed pellet | N/A | None</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Source: Sampling Unit Selection module</t>
+          <t>Source: Core module</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1691,51 +1691,91 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Sampling Unit Selection Criteria</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The rules governing which sampling unit(s) within a sample are selected for analysis, and why. Covers the criteria applied when choosing grains, aliquots, spots, or a region of interest — size, morphology, clarity, freedom from inclusions or alteration, phase identity, or spatial position. Distinct from Target Material, which states the material type the procedure is designed for, and from Sampling Unit, which names the kind of subdivision one row of reported values corresponds to: this field states how, within such a sample, the unit actually analysed is picked out.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Source: Sampling Unit Selection module</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Pre-Analysis Imaging and Screening</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Imaging or other characterisation performed before the measurement in order to select or locate the sampling unit to be analysed, including the technique, instrument and settings used, and how individual analyses are linked back to the images. Distinct from any imaging the procedure performs as its own measurement. Where the imaging is performed on a separate instrument, it should also be recorded in the Group 1 coupling fields.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Source: Sampling Unit Selection module</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
       <c r="L30" t="inlineStr">
         <is>
           <t>N</t>
@@ -1743,16 +1783,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3. Instrument &amp; Software</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>N</t>
@@ -1762,64 +1792,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Instrument Manufacturer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Manufacturer of the instrument that performs the measurement, recorded as a controlled value. Where a procedure couples a sample-introduction system to an analysing instrument, this records the analysing instrument. Instrument Model gives the specific designation.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Controlled list</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>WITec | Renishaw | HORIBA | Bruker | Thermo Fisher Scientific | Custom-built | Unknown | N/A | None</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>(none)</t>
+          <t>3. Instrument &amp; Software</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Bruker</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Instrument Model</t>
+          <t>Instrument Manufacturer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Model designation of the instrument that performs the measurement, including any generation or configuration suffix. Conventionally written with the manufacturer name included; Instrument Manufacturer records the vendor separately, as a controlled value, so that procedures remain findable by vendor.</t>
+          <t>Manufacturer of the instrument that performs the measurement, recorded as a controlled value. Where a procedure couples a sample-introduction system to an analysing instrument, this records the analysing instrument. Instrument Model gives the specific designation.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1834,12 +1829,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>Controlled list</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>e.g., 'alpha 300 R'</t>
+          <t>WITec | Renishaw | HORIBA | Bruker | Thermo Fisher Scientific | Custom-built | Unknown | N/A | None</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1859,19 +1854,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Bruker MultiMode 8</t>
+          <t>Bruker</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Acquisition Software</t>
+          <t>Instrument Model</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Instrument control, automation and data acquisition software used to collect the raw data, including version number. Distinct from Data Processing Software(s), which covers everything applied to the data after acquisition.</t>
+          <t>Model designation of the instrument that performs the measurement, including any generation or configuration suffix. Conventionally written with the manufacturer name included; Instrument Manufacturer records the vendor separately, as a controlled value, so that procedures remain findable by vendor.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1881,7 +1876,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Editable</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1891,7 +1886,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>e.g., 'WITec Control FIVE 5.3'</t>
+          <t>e.g., 'alpha 300 R'</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1911,63 +1906,108 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Bruker MultiMode 8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Acquisition Software</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Instrument control, automation and data acquisition software used to collect the raw data, including version number. Distinct from Data Processing Software(s), which covers everything applied to the data after acquisition.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>e.g., 'WITec Control FIVE 5.3'</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Data Processing Software(s)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>All software applied to the data after acquisition in order to produce the reported quantities, including version numbers. List every package used. Distinct from Acquisition Software, which controls the instrument and collects the raw data.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>e.g., 'WITec Project FIVE 5.3'</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>N</t>
@@ -1975,16 +2015,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>4. Measurement Information</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>N</t>
@@ -1994,52 +2024,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytical Mode</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary analytical mode(s) executed under this procedure. Records one value for a single-mode procedure and all applicable modes for a multi-mode one. Applies even where a procedure defines no mode flag columns.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Controlled list</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Point spectrum</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability.</t>
+          <t>4. Measurement Information</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2051,68 +2041,108 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Analytical Mode</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Primary analytical mode(s) executed under this procedure. Records one value for a single-mode procedure and all applicable modes for a multi-mode one. Applies even where a procedure defines no mode flag columns.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Point spectrum</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Reported Variables and Units</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>The final variable(s) this procedure reports and their units — distinct from the fields recording what was *acquired* rather than what is reported. Record every reported variable, including intermediate quantities reported alongside final ones (e.g. both the 206Pb/238U ratio and the 206Pb/238U date). Where a reported variable is a nominal property with no magnitude (e.g. a mineral identification), record the variable and give the unit as 'N/A — nominal property'.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Calc_Ramp_Ex_nm | Calc_Ramp_Rt_nm | Defl_V_Ex | Defl_V_Rt</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>5. Data Processing</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>N</t>
@@ -2122,42 +2152,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Calibration Factor and Determination Method</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>An externally-calibrated factor that converts the measured quantity into the reported quantity, how it was determined, and its uncertainty. Applies where the conversion depends on a factor calibrated against a reference of independently known value, rather than on the instrument response alone. Distinct from the fields that name the calibration material and that state which approach applies to which analyte, where the technique has them: this field records the resulting factor itself.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Text (free)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Source: Calibration Factor module</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>reported property</t>
+          <t>5. Data Processing</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2169,56 +2169,96 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Calibration Factor and Determination Method</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>An externally-calibrated factor that converts the measured quantity into the reported quantity, how it was determined, and its uncertainty. Applies where the conversion depends on a factor calibrated against a reference of independently known value, rather than on the instrument response alone. Distinct from the fields that name the calibration material and that state which approach applies to which analyte, where the technique has them: this field records the resulting factor itself.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Source: Calibration Factor module</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>reported property</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Constants and Reference Values Used</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Physical constants and reference values used in data reduction to calculate the final reported quantity (e.g., decay constants for age calculation, standard isotope ratios, or other citable reference values used in a correction or calculation), together with their source. Distinct from the Group 6 reference-material fields, which document accepted values for specific calibration/validation materials rather than universal physical constants. Record "None" if no citable, revisable physical constants feed into this procedure's data reduction.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>e.g., 'ICDD PDF-4+ 2024 reference patterns'</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>N</t>
@@ -2226,16 +2266,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>6. Quality Control &amp; Uncertainty</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>N</t>
@@ -2245,52 +2275,69 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>6. Quality Control &amp; Uncertainty</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Additional Notes</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Any procedure- or analysis-specific information not captured by a structured field anywhere in this TAPP — including anomalies, deviations from the registered procedure, instrument modifications, and supplementary context. Scope is the whole document, not Group 6: this is the last field of the TAPP and covers all six groups. Use sparingly; a structured field is preferred for anything that can be formally categorised.</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="L48" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2410,8 +2457,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -2448,7 +2493,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -2533,9 +2577,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
